--- a/TalentMaster_HH_Testit_v8_bright.xlsx
+++ b/TalentMaster_HH_Testit_v8_bright.xlsx
@@ -11229,11 +11229,11 @@
   <dimension ref="A1:BH54"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
-    <col width="13" customWidth="1" style="25" min="1" max="1"/>
-    <col width="13" customWidth="1" style="25" min="2" max="2"/>
+    <col width="14" customWidth="1" style="25" min="1" max="1"/>
+    <col width="14" customWidth="1" style="25" min="2" max="2"/>
     <col width="11" customWidth="1" style="25" min="3" max="3"/>
     <col width="11" customWidth="1" style="25" min="4" max="4"/>
-    <col width="13" customWidth="1" style="25" min="5" max="5"/>
+    <col width="14" customWidth="1" style="25" min="5" max="5"/>
     <col width="11" customWidth="1" style="25" min="6" max="6"/>
     <col width="11" customWidth="1" style="25" min="7" max="7"/>
     <col width="7" customWidth="1" style="25" min="8" max="11"/>
@@ -18422,14 +18422,6 @@
       <c r="BH54" s="67" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="A2:BH2"/>
-    <mergeCell ref="A1:BH1"/>
-    <mergeCell ref="A2:AD2"/>
-    <mergeCell ref="A3:AB3"/>
-    <mergeCell ref="A3:BH3"/>
-    <mergeCell ref="A1:AD1"/>
-  </mergeCells>
   <dataValidations count="1">
     <dataValidation sqref="D5:D44" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Virhe" error="Käytä P tai T" type="list" errorStyle="stop" operator="between">
       <formula1>"P,T"</formula1>
